--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-02).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-163</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>R$ 1.674.923,38</t>
-  </si>
-  <si>
-    <t>R$ 9.681,64
-R$ 9.889,87</t>
-  </si>
-  <si>
-    <t>12.1%
-14.5%</t>
-  </si>
-  <si>
-    <t>101.9</t>
+166</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 1.705.397,12</t>
+  </si>
+  <si>
+    <t>R$ 9.689,76
+R$ 9.894,71</t>
+  </si>
+  <si>
+    <t>12.2%
+14.6%</t>
+  </si>
+  <si>
+    <t>102.0</t>
   </si>
   <si>
     <t>6.4%</t>
   </si>
   <si>
-    <t>35.5%</t>
-  </si>
-  <si>
-    <t>(11.5%)</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>45.3%</t>
+  </si>
+  <si>
+    <t>(1.3%)</t>
+  </si>
+  <si>
+    <t>2.5%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>31.2</t>
-  </si>
-  <si>
-    <t>54.3%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>8.7</t>
-  </si>
-  <si>
-    <t>15.6</t>
-  </si>
-  <si>
-    <t>22.4</t>
-  </si>
-  <si>
-    <t>56.6%</t>
-  </si>
-  <si>
-    <t>-R$ 38.037,14</t>
+    <t>31.3</t>
+  </si>
+  <si>
+    <t>54.0%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>8.8</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>22.6</t>
+  </si>
+  <si>
+    <t>56.3%</t>
+  </si>
+  <si>
+    <t>-R$ 37.772,94</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,59 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
+      <c r="O13" s="5">
+        <v>15512</v>
+      </c>
+      <c r="P13" s="5">
+        <v>15512</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.10039001703930395</v>
+      </c>
+      <c r="R13" s="7">
+        <v>162</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.072847682119205226</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.41555143759669938</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.06542508380608561</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.020899355337802992</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.015176689014956163</v>
+      </c>
+      <c r="X13" s="8">
+        <v>37.612307692307695</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.48461538461538461</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>14.067272727272726</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>7.4516669230769228</v>
+      </c>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="AD13" s="8">
+        <v>29.772307692307692</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.36153846153846153</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>264.19999999999999</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3120,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>6.1651993710691828</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>19.696135999999999</v>
+      </c>
       <c r="AD14" s="8">
         <v>26.538333125000001</v>
       </c>
@@ -5011,7 +5047,9 @@
       <c r="AB29" s="8">
         <v>24.227017894736839</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>32.750067000000001</v>
+      </c>
       <c r="AD29" s="8">
         <v>40.88894736842105</v>
       </c>
@@ -6247,7 +6285,9 @@
       <c r="AB39" s="8">
         <v>6.280951948051948</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>8.9107430000000001</v>
+      </c>
       <c r="AD39" s="8">
         <v>16.6299582278481</v>
       </c>
@@ -6733,7 +6773,9 @@
       <c r="AB43" s="8">
         <v>13.504166666666666</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>19.439813999999998</v>
+      </c>
       <c r="AD43" s="8">
         <v>26.375</v>
       </c>
@@ -6862,7 +6904,9 @@
       <c r="AB44" s="8">
         <v>4.0986666666666665</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>7.2102880000000003</v>
+      </c>
       <c r="AD44" s="8">
         <v>15.069078947368421</v>
       </c>
@@ -7638,7 +7682,9 @@
       <c r="AB50" s="8">
         <v>9.630054918032787</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>12.544301000000001</v>
+      </c>
       <c r="AD50" s="8">
         <v>20.247580645161289</v>
       </c>
@@ -8122,7 +8168,9 @@
       <c r="AB54" s="8">
         <v>15.558333333333334</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>22.809401000000001</v>
+      </c>
       <c r="AD54" s="8">
         <v>29.717948717948719</v>
       </c>
@@ -8251,7 +8299,9 @@
       <c r="AB55" s="8">
         <v>15.997154878048779</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>19.596122999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>26.137103571428572</v>
       </c>
@@ -8378,7 +8428,9 @@
       <c r="AB56" s="8">
         <v>4.1284482758620689</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>11.630209000000001</v>
+      </c>
       <c r="AD56" s="8">
         <v>19.683471074380165</v>
       </c>
@@ -10217,7 +10269,9 @@
       <c r="AB71" s="8">
         <v>4.8113636363636365</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>9.2397310000000008</v>
+      </c>
       <c r="AD71" s="8">
         <v>16.747517021276597</v>
       </c>
@@ -10344,7 +10398,9 @@
       <c r="AB72" s="8">
         <v>6.9914730232558142</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>15.855613999999999</v>
+      </c>
       <c r="AD72" s="8">
         <v>22.703023255813953</v>
       </c>
@@ -10693,7 +10749,9 @@
       <c r="AB75" s="8">
         <v>5.1794433333333334</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>11.922454</v>
+      </c>
       <c r="AD75" s="8">
         <v>18.532258064516128</v>
       </c>
@@ -12454,7 +12512,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12490,25 +12548,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>8103.5299999999997</v>
+      </c>
+      <c r="P90" s="5">
+        <v>8103.5299999999997</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.41907278598496789</v>
+      </c>
+      <c r="R90" s="7">
+        <v>79</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.067567567567567544</v>
+      </c>
+      <c r="T90" s="6">
+        <v>20.385527677444273</v>
+      </c>
+      <c r="U90" s="6">
+        <v>20.385527677444273</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.015921888362232264</v>
+      </c>
+      <c r="W90" s="6">
+        <v>-0.010449335042876377</v>
+      </c>
+      <c r="X90" s="8">
+        <v>45.54032258064516</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.72580645161290325</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>14.025406097560976</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>21.194624193548389</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>35.745905</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>42.885483870967747</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.17741935483870969</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>0</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -13607,10 +13701,10 @@
         <v>0.21739130434782616</v>
       </c>
       <c r="T99" s="6">
-        <v>-0.13973380421414941</v>
+        <v>0.24403547068266673</v>
       </c>
       <c r="U99" s="6">
-        <v>-0.39669907870297283</v>
+        <v>-0.012929803806156662</v>
       </c>
       <c r="V99" s="6">
         <v>0.01250679717237629</v>
@@ -13633,7 +13727,9 @@
       <c r="AB99" s="8">
         <v>16.496407758620691</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>26.244147999999999</v>
+      </c>
       <c r="AD99" s="8">
         <v>32.841525423728818</v>
       </c>
@@ -13944,7 +14040,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13980,25 +14076,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>6858.21</v>
+      </c>
+      <c r="P102" s="5">
+        <v>6858.21</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.20228564015630268</v>
+      </c>
+      <c r="R102" s="7">
+        <v>77</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.11594202898550732</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.34199885976078304</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.018062439032925502</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0013277517019747134</v>
+      </c>
+      <c r="X102" s="8">
+        <v>26.413332727272728</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.12727272727272726</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.7989716049382709</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>6.9260416666666664</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>18.919090909090908</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.69090909090909092</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -14508,7 +14638,9 @@
       <c r="AB106" s="8">
         <v>1.4345536585365852</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>5.9670909999999999</v>
+      </c>
       <c r="AD106" s="8">
         <v>12.939024390243903</v>
       </c>
@@ -14859,7 +14991,9 @@
       <c r="AB109" s="8">
         <v>29.549478125</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>35.693229000000002</v>
+      </c>
       <c r="AD109" s="8">
         <v>43.622396875</v>
       </c>
@@ -15081,7 +15215,9 @@
       <c r="AB111" s="8">
         <v>1.075</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>4.9694440000000002</v>
+      </c>
       <c r="AD111" s="8">
         <v>11.944450000000002</v>
       </c>
@@ -16700,7 +16836,9 @@
       <c r="AB124" s="8">
         <v>26.589583333333334</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>32.246527</v>
+      </c>
       <c r="AD124" s="8">
         <v>40.205554166666666</v>
       </c>
@@ -19333,7 +19471,9 @@
       <c r="AB145" s="8">
         <v>3.8007085106382976</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>11.929411999999999</v>
+      </c>
       <c r="AD145" s="8">
         <v>16.396990277777778</v>
       </c>
@@ -19857,7 +19997,9 @@
       <c r="AB149" s="8">
         <v>5.8583499999999997</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>11.887499</v>
+      </c>
       <c r="AD149" s="8">
         <v>17.449999999999999</v>
       </c>
@@ -21184,7 +21326,9 @@
       <c r="AB160" s="8">
         <v>19.365476190476191</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>26.191057000000001</v>
+      </c>
       <c r="AD160" s="8">
         <v>33.107539285714289</v>
       </c>
@@ -22797,7 +22941,9 @@
       <c r="AB173" s="8">
         <v>14.81875</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>23.422083000000001</v>
+      </c>
       <c r="AD173" s="8">
         <v>20.403030303030302</v>
       </c>
@@ -23057,7 +23203,9 @@
       <c r="AB175" s="8">
         <v>2.5429499999999998</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>14.191798</v>
+      </c>
       <c r="AD175" s="8">
         <v>20.610344827586207</v>
       </c>
@@ -23831,7 +23979,9 @@
       <c r="AB181" s="8">
         <v>0.86754210526315789</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>6.2962949999999998</v>
+      </c>
       <c r="AD181" s="8">
         <v>13.064368965517241</v>
       </c>
@@ -24577,7 +24727,9 @@
       <c r="AB187" s="8">
         <v>9.8300000000000001</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>14.992222</v>
+      </c>
       <c r="AD187" s="8">
         <v>21.956666666666667</v>
       </c>
@@ -24839,7 +24991,9 @@
       <c r="AB189" s="8">
         <v>13.476785714285715</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>17.877934</v>
+      </c>
       <c r="AD189" s="8">
         <v>24.180746551724141</v>
       </c>
@@ -25750,7 +25904,9 @@
       <c r="AB196" s="8">
         <v>20.353335000000001</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>35.662855999999998</v>
+      </c>
       <c r="AD196" s="8">
         <v>41.326190476190476</v>
       </c>
@@ -26272,7 +26428,9 @@
       <c r="AB200" s="8">
         <v>3.5166666666666666</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>11.884999000000001</v>
+      </c>
       <c r="AD200" s="8">
         <v>17.25</v>
       </c>
@@ -26845,7 +27003,9 @@
       <c r="AB205" s="8">
         <v>7.1324578947368416</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>11.479281</v>
+      </c>
       <c r="AD205" s="8">
         <v>17.492857142857144</v>
       </c>
@@ -26970,7 +27130,9 @@
       <c r="AB206" s="8">
         <v>6.9758349999999991</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>15.02962</v>
+      </c>
       <c r="AD206" s="8">
         <v>21.941271428571429</v>
       </c>
